--- a/artfynd/A 29683-2023 artfynd.xlsx
+++ b/artfynd/A 29683-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29683-2023 artfynd.xlsx
+++ b/artfynd/A 29683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63639018</v>
+        <v>112276240</v>
       </c>
       <c r="B2" t="n">
-        <v>107952</v>
+        <v>109501</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -709,19 +709,23 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>400m SO-SSO Köle vägkorsn, Sk</t>
+          <t>Köle vägkorsning, 400 m SSO , Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448504.9137814625</v>
+        <v>448505</v>
       </c>
       <c r="R2" t="n">
-        <v>6185263.791546612</v>
+        <v>6185264</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,29 +747,24 @@
           <t>Maglehem</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Kri-0111</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2003-05-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-05-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Valeriana dioica/2D7j3030/Maglehem s:n/ÅWg/ /Åke Widgren,Karlskrona</t>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,23 +773,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>björksumpskog, rikl.</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    797635</t>
+          <t>Björksumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -799,132 +794,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>112276240</v>
-      </c>
-      <c r="B3" t="n">
-        <v>109501</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Småvänderot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Valeriana dioica</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Köle vägkorsning, 400 m SSO , Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>448505</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6185264</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Maglehem</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>M-Kri-0111</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2003-05-29</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2003-05-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Björksumpskog</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Åke Widgren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
